--- a/application/views/template/sistema/archivos/excel/productos_reposicion_carga/productos_reposicion_carga.xlsx
+++ b/application/views/template/sistema/archivos/excel/productos_reposicion_carga/productos_reposicion_carga.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\clubdelpintoraxaltaguatemala\application\views\template\sistema\archivos\excel\productos_reposicion_carga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\strategix\php-7.4.27\clubdelpintoraxaltabrasil\application\views\template\sistema\archivos\excel\productos_reposicion_carga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1213ADE5-5103-4A53-9EE2-FB8EC94C95A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818B95FF-851E-4512-80F5-F1AF0112FD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="480" windowWidth="52575" windowHeight="15450" xr2:uid="{C9241849-8C11-46F3-9B8B-BF5EA5B89F9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C9241849-8C11-46F3-9B8B-BF5EA5B89F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,16 +40,16 @@
     <t>GMS</t>
   </si>
   <si>
-    <t>Precio</t>
-  </si>
-  <si>
-    <t>Descripción</t>
-  </si>
-  <si>
     <t>Código</t>
   </si>
   <si>
-    <t>Presentación</t>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Apresentação</t>
+  </si>
+  <si>
+    <t>Preço</t>
   </si>
 </sst>
 </file>
@@ -133,9 +133,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -173,7 +173,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -279,7 +279,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -421,7 +421,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -430,16 +430,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0087433F-6E7A-4F5F-B347-C1F65D17F84B}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -447,13 +447,13 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/application/views/template/sistema/archivos/excel/productos_reposicion_carga/productos_reposicion_carga.xlsx
+++ b/application/views/template/sistema/archivos/excel/productos_reposicion_carga/productos_reposicion_carga.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\strategix\php-7.4.27\clubdelpintoraxaltabrasil\application\views\template\sistema\archivos\excel\productos_reposicion_carga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\strategix\php_7.4.27\clubdelpintoraxaltabrasil\application\views\template\sistema\archivos\excel\productos_reposicion_carga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818B95FF-851E-4512-80F5-F1AF0112FD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA84E4E-8AB1-4655-B29D-7158232CAC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C9241849-8C11-46F3-9B8B-BF5EA5B89F9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C9241849-8C11-46F3-9B8B-BF5EA5B89F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,16 +64,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82127"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -81,12 +94,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -121,6 +150,11 @@
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="FFC82127"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -443,16 +477,16 @@
       <c r="A1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/application/views/template/sistema/archivos/excel/productos_reposicion_carga/productos_reposicion_carga.xlsx
+++ b/application/views/template/sistema/archivos/excel/productos_reposicion_carga/productos_reposicion_carga.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\strategix\php_7.4.27\clubdelpintoraxaltabrasil\application\views\template\sistema\archivos\excel\productos_reposicion_carga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA84E4E-8AB1-4655-B29D-7158232CAC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{027FF788-30AE-4F13-A7A6-10E751A3899E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C9241849-8C11-46F3-9B8B-BF5EA5B89F9B}"/>
   </bookViews>
@@ -113,9 +113,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,7 +475,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
